--- a/templates/TemplateTicketsCNP.xlsx
+++ b/templates/TemplateTicketsCNP.xlsx
@@ -4,6 +4,7 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Production" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Template" sheetId="2" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -11,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="49">
   <si>
     <t>Du 02/01/2026 00:00:00 au 09/01/2026 00:00:00</t>
   </si>
@@ -85,6 +86,9 @@
     <t>LOGISTIQUE</t>
   </si>
   <si>
+    <t>MOBILIER</t>
+  </si>
+  <si>
     <t>PHOTOCOPIEURS</t>
   </si>
   <si>
@@ -95,6 +99,66 @@
   </si>
   <si>
     <t>Total Géneral</t>
+  </si>
+  <si>
+    <t>Du {{Date1}} au {{Date2}}</t>
+  </si>
+  <si>
+    <t>{{BATIMENT}}</t>
+  </si>
+  <si>
+    <t>{{ACCES_ET_SECURITE}}</t>
+  </si>
+  <si>
+    <t>{{CLIMATISATION_ET_CHAUFFAGE}}</t>
+  </si>
+  <si>
+    <t>{{ELECTRICITE}}</t>
+  </si>
+  <si>
+    <t>{{PLOMBERIE}}</t>
+  </si>
+  <si>
+    <t>{{ASCENSEURS}}</t>
+  </si>
+  <si>
+    <t>{{EQUIPEMENTS_SPECIFIQUES}}</t>
+  </si>
+  <si>
+    <t>{{Application}}</t>
+  </si>
+  <si>
+    <t>{{MLT_TOTAL}}</t>
+  </si>
+  <si>
+    <t>{{DISTRIBUTEUR_DE_BOISSONS}}</t>
+  </si>
+  <si>
+    <t>{{GESTION_DES_DECHETS}}</t>
+  </si>
+  <si>
+    <t>{{SERVICES}}</t>
+  </si>
+  <si>
+    <t>{{LOGISTIQUE}}</t>
+  </si>
+  <si>
+    <t>{{MOBILIER}}</t>
+  </si>
+  <si>
+    <t>{{PHOTOCOPIEURS}}</t>
+  </si>
+  <si>
+    <t>{{AMENAGEMENT_POSTE_TRAVAIL_HAND}}</t>
+  </si>
+  <si>
+    <t>{{PROPRETE}}</t>
+  </si>
+  <si>
+    <t>{{MLS_TOTAL}}</t>
+  </si>
+  <si>
+    <t>{{TOTAL}}</t>
   </si>
 </sst>
 </file>
@@ -278,6 +342,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -824,7 +892,7 @@
     </row>
     <row r="16">
       <c r="B16" s="13" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="12">
         <v>0.0</v>
@@ -847,7 +915,7 @@
     </row>
     <row r="17">
       <c r="B17" s="13" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="12">
         <v>0.0</v>
@@ -870,7 +938,7 @@
     </row>
     <row r="18">
       <c r="B18" s="13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C18" s="12">
         <v>0.0</v>
@@ -893,7 +961,7 @@
     </row>
     <row r="19">
       <c r="B19" s="13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" s="12">
         <v>0.0</v>
@@ -928,10 +996,478 @@
     <row r="22">
       <c r="F22" s="16"/>
       <c r="G22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A3:A10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:A19"/>
+    <mergeCell ref="A20:B20"/>
+  </mergeCells>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="1" max="1" width="29.88"/>
+    <col customWidth="1" min="2" max="2" width="34.88"/>
+    <col customWidth="1" min="3" max="3" width="29.25"/>
+    <col customWidth="1" min="4" max="4" width="24.25"/>
+    <col customWidth="1" min="5" max="5" width="23.38"/>
+    <col customWidth="1" min="7" max="7" width="13.88"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="18.75" customHeight="1">
+      <c r="A1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="2"/>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G3" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H3" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H4" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G5" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H5" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G6" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H6" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="D8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G8" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H8" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G9" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H9" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G13" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H14" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="D15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G15" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H15" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="D16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G16" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H16" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="D17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G17" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H17" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G18" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H18" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="H22" s="15">
-        <v>0.0</v>
+      <c r="C19" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="D19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="E19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="F19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="G19" s="12">
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="12">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="15" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="F22" s="16"/>
+      <c r="G22" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="H22" s="15" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
